--- a/Тест2/209.xlsx
+++ b/Тест2/209.xlsx
@@ -234,16 +234,16 @@
     <t xml:space="preserve">Gemolizin (sfingomielinaza)</t>
   </si>
   <si>
-    <t xml:space="preserve">Klassik ekzotoksin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qalin kapsula qobig'i</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Xivchin tolasi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spora po'sti</t>
+    <t xml:space="preserve">Klassik ekzotoksin (botulin)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qalin kapsula qobig'i (Burri)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xivchin tolasi (flagellin)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spora po'sti (dipikolinat)</t>
   </si>
   <si>
     <t xml:space="preserve">To'g'ri javob: Gemolizin (sfingomielinaza). Leptospiralar klassik ekzotoksin hosil qilmaydi, ammo gemolizinlar, jumladan sfingomielinaza, muhim. Manba: Mavzu materiali (209.docx); Riedel S. va boshq. Jawetz, Melnick &amp; Adelberg's Medical Microbiology, 28-nashr (2019).</t>
